--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDAufnahmeBundle.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDAufnahmeBundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T12:12:39+00:00</t>
+    <t>2024-11-05T09:00:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDAufnahmeBundle.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDAufnahmeBundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T09:00:17+00:00</t>
+    <t>2024-11-05T09:16:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDAufnahmeBundle.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDAufnahmeBundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T09:16:22+00:00</t>
+    <t>2024-11-05T10:26:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDAufnahmeBundle.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDAufnahmeBundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T10:26:22+00:00</t>
+    <t>2024-11-06T09:40:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDAufnahmeBundle.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDAufnahmeBundle.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7524" uniqueCount="478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7524" uniqueCount="482">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T09:40:37+00:00</t>
+    <t>2024-11-07T06:21:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -608,8 +608,8 @@
     <t>An entry in a bundle resource - will either contain a resource or information about a resource (transactions and history only).</t>
   </si>
   <si>
-    <t xml:space="preserve">type:resource}
-</t>
+    <t>type:resource}
+profile:resolve()}</t>
   </si>
   <si>
     <t>open</t>
@@ -1278,6 +1278,19 @@
   </si>
   <si>
     <t>Bundle.entry:Hauptversicherter.resource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RelatedPerson {http://example.org/StructureDefinition/Hauptversicherter}
+</t>
+  </si>
+  <si>
+    <t>A person that is related to a patient, but who is not a direct target of care</t>
+  </si>
+  <si>
+    <t>Information about a person that is involved in a patient's health or the care for a patient, but who is not the target of healthcare, nor has a formal responsibility in the care process.</t>
+  </si>
+  <si>
+    <t>Entity, Role, or Act,role</t>
   </si>
   <si>
     <t>Bundle.entry:Hauptversicherter.search</t>
@@ -18862,7 +18875,7 @@
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
-        <v>362</v>
+        <v>20</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
@@ -18881,13 +18894,13 @@
         <v>20</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>363</v>
+        <v>402</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>364</v>
+        <v>403</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>365</v>
+        <v>404</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
@@ -18959,15 +18972,15 @@
         <v>20</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>367</v>
+        <v>405</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>368</v>
+        <v>20</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B152" t="s" s="2">
         <v>204</v>
@@ -19079,7 +19092,7 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B153" t="s" s="2">
         <v>208</v>
@@ -19191,7 +19204,7 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="B154" t="s" s="2">
         <v>209</v>
@@ -19305,7 +19318,7 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="B155" t="s" s="2">
         <v>210</v>
@@ -19421,7 +19434,7 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="B156" t="s" s="2">
         <v>211</v>
@@ -19535,7 +19548,7 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="B157" t="s" s="2">
         <v>217</v>
@@ -19649,7 +19662,7 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B158" t="s" s="2">
         <v>222</v>
@@ -19761,7 +19774,7 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="B159" t="s" s="2">
         <v>226</v>
@@ -19873,7 +19886,7 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B160" t="s" s="2">
         <v>227</v>
@@ -19987,7 +20000,7 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B161" t="s" s="2">
         <v>228</v>
@@ -20103,7 +20116,7 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="B162" t="s" s="2">
         <v>229</v>
@@ -20215,7 +20228,7 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="B163" t="s" s="2">
         <v>235</v>
@@ -20329,7 +20342,7 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B164" t="s" s="2">
         <v>239</v>
@@ -20441,7 +20454,7 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="B165" t="s" s="2">
         <v>242</v>
@@ -20553,7 +20566,7 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="B166" t="s" s="2">
         <v>245</v>
@@ -20665,7 +20678,7 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="B167" t="s" s="2">
         <v>248</v>
@@ -20777,7 +20790,7 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="B168" t="s" s="2">
         <v>251</v>
@@ -20889,7 +20902,7 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="B169" t="s" s="2">
         <v>255</v>
@@ -21001,7 +21014,7 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="B170" t="s" s="2">
         <v>256</v>
@@ -21115,7 +21128,7 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B171" t="s" s="2">
         <v>257</v>
@@ -21231,7 +21244,7 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B172" t="s" s="2">
         <v>258</v>
@@ -21343,7 +21356,7 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B173" t="s" s="2">
         <v>261</v>
@@ -21455,7 +21468,7 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="B174" t="s" s="2">
         <v>264</v>
@@ -21569,7 +21582,7 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="B175" t="s" s="2">
         <v>268</v>
@@ -21683,7 +21696,7 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="B176" t="s" s="2">
         <v>272</v>
@@ -21797,13 +21810,13 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="B177" t="s" s="2">
         <v>181</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="D177" t="s" s="2">
         <v>20</v>
@@ -21911,7 +21924,7 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="B178" t="s" s="2">
         <v>188</v>
@@ -22023,7 +22036,7 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="B179" t="s" s="2">
         <v>189</v>
@@ -22137,7 +22150,7 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B180" t="s" s="2">
         <v>190</v>
@@ -22253,7 +22266,7 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B181" t="s" s="2">
         <v>191</v>
@@ -22365,7 +22378,7 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B182" t="s" s="2">
         <v>194</v>
@@ -22479,7 +22492,7 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="B183" t="s" s="2">
         <v>199</v>
@@ -22505,13 +22518,13 @@
         <v>20</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" s="2"/>
@@ -22577,13 +22590,13 @@
         <v>20</v>
       </c>
       <c r="AK183" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="AL183" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="AM183" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="AN183" t="s" s="2">
         <v>20</v>
@@ -22591,7 +22604,7 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="B184" t="s" s="2">
         <v>204</v>
@@ -22703,7 +22716,7 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="B185" t="s" s="2">
         <v>208</v>
@@ -22815,7 +22828,7 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B186" t="s" s="2">
         <v>209</v>
@@ -22929,7 +22942,7 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="B187" t="s" s="2">
         <v>210</v>
@@ -23045,7 +23058,7 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="B188" t="s" s="2">
         <v>211</v>
@@ -23159,7 +23172,7 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="B189" t="s" s="2">
         <v>217</v>
@@ -23273,7 +23286,7 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="B190" t="s" s="2">
         <v>222</v>
@@ -23385,7 +23398,7 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="B191" t="s" s="2">
         <v>226</v>
@@ -23497,7 +23510,7 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="B192" t="s" s="2">
         <v>227</v>
@@ -23611,7 +23624,7 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="B193" t="s" s="2">
         <v>228</v>
@@ -23727,7 +23740,7 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="B194" t="s" s="2">
         <v>229</v>
@@ -23839,7 +23852,7 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="B195" t="s" s="2">
         <v>235</v>
@@ -23953,7 +23966,7 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B196" t="s" s="2">
         <v>239</v>
@@ -24065,7 +24078,7 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="B197" t="s" s="2">
         <v>242</v>
@@ -24177,7 +24190,7 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="B198" t="s" s="2">
         <v>245</v>
@@ -24289,7 +24302,7 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="B199" t="s" s="2">
         <v>248</v>
@@ -24401,7 +24414,7 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="B200" t="s" s="2">
         <v>251</v>
@@ -24513,7 +24526,7 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="B201" t="s" s="2">
         <v>255</v>
@@ -24625,7 +24638,7 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B202" t="s" s="2">
         <v>256</v>
@@ -24739,7 +24752,7 @@
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B203" t="s" s="2">
         <v>257</v>
@@ -24855,7 +24868,7 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="B204" t="s" s="2">
         <v>258</v>
@@ -24967,7 +24980,7 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="B205" t="s" s="2">
         <v>261</v>
@@ -25079,7 +25092,7 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="B206" t="s" s="2">
         <v>264</v>
@@ -25193,7 +25206,7 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="B207" t="s" s="2">
         <v>268</v>
@@ -25307,7 +25320,7 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B208" t="s" s="2">
         <v>272</v>
@@ -25421,10 +25434,10 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -25447,19 +25460,19 @@
         <v>89</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="N209" t="s" s="2">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="O209" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="P209" t="s" s="2">
         <v>20</v>
@@ -25508,7 +25521,7 @@
         <v>20</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>77</v>
@@ -25537,10 +25550,10 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -25563,16 +25576,16 @@
         <v>89</v>
       </c>
       <c r="K210" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="N210" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="O210" s="2"/>
       <c r="P210" t="s" s="2">
@@ -25622,7 +25635,7 @@
         <v>20</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>77</v>
@@ -25631,7 +25644,7 @@
         <v>88</v>
       </c>
       <c r="AI210" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="AJ210" t="s" s="2">
         <v>20</v>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDAufnahmeBundle.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDAufnahmeBundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-07T06:21:30+00:00</t>
+    <t>2024-11-07T13:12:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDAufnahmeBundle.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDAufnahmeBundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-07T13:12:32+00:00</t>
+    <t>2024-11-07T14:31:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDAufnahmeBundle.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDAufnahmeBundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-07T14:31:26+00:00</t>
+    <t>2024-11-08T06:37:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDAufnahmeBundle.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDAufnahmeBundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T06:16:09+00:00</t>
+    <t>2024-11-12T07:45:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -925,7 +925,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Encounter {http://example.org/StructureDefinition/MOPEDEncounter}
+    <t xml:space="preserve">Encounter {http://example.org/StructureDefinition/MOPEDEncounterKH}
 </t>
   </si>
   <si>
@@ -1040,7 +1040,7 @@
     <t>Bundle.entry:Coverage.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Coverage {http://example.org/StructureDefinition/SVCCoverage}
+    <t xml:space="preserve">Coverage {http://example.org/StructureDefinition/MOPEDCoverage}
 </t>
   </si>
   <si>
@@ -1368,28 +1368,28 @@
     <t>Bundle.entry:Hauptversicherter.response.outcome</t>
   </si>
   <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation</t>
-  </si>
-  <si>
-    <t>ÜberweisendeOrganisation</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.id</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.extension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.modifierExtension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.link</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.fullUrl</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.resource</t>
+    <t>Bundle.entry:UeberweisendeOrganisation</t>
+  </si>
+  <si>
+    <t>UeberweisendeOrganisation</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.link</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.fullUrl</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.resource</t>
   </si>
   <si>
     <t xml:space="preserve">Organization {http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-organization}
@@ -1411,79 +1411,79 @@
     <t>Entity, Role, or Act,Organization(classCode=ORG, determinerCode=INST)</t>
   </si>
   <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.search</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.search.id</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.search.extension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.search.modifierExtension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.search.mode</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.search.score</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.request</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.request.id</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.request.extension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.request.modifierExtension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.request.method</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.request.url</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.request.ifNoneMatch</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.request.ifModifiedSince</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.request.ifMatch</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.request.ifNoneExist</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.response</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.response.id</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.response.extension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.response.modifierExtension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.response.status</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.response.location</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.response.etag</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.response.lastModified</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.response.outcome</t>
+    <t>Bundle.entry:UeberweisendeOrganisation.search</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.search.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.search.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.search.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.search.mode</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.search.score</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.request</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.request.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.request.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.request.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.request.method</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.request.url</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.request.ifNoneMatch</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.request.ifModifiedSince</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.request.ifMatch</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.request.ifNoneExist</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.response</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.response.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.response.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.response.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.response.status</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.response.location</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.response.etag</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.response.lastModified</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.response.outcome</t>
   </si>
   <si>
     <t>Bundle.signature</t>
@@ -1827,9 +1827,9 @@
   <dimension ref="A1:AN210"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="64.4296875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="65.55859375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="39.0078125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="25.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="26.98046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="28.78515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
